--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardSkills" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Levels" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance_View" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cards" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CardSkills" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Levels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Decks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance_View" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$I$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,138 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mini_pekka_body</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>迷你皮卡</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D7" t="n">
+        <v>320</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>musketeer_body</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>火枪手</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>340</v>
+      </c>
+      <c r="D8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>skeleton_body</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>骷髅</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>baby_dragon_body</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小龙</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>900</v>
+      </c>
+      <c r="D10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
@@ -682,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -917,6 +1049,150 @@
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mini_pekka</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>迷你皮卡</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>musketeer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>火枪手</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeletons</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>骷髅海</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>baby_dragon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小龙</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>闪电</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>滚木</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -929,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1203,6 +1479,166 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mini_pekka</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mini_pekka_body</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>musketeer</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>musketeer_body</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeletons</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>skeleton_body</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>baby_dragon</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>baby_dragon_body</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>direct_damage</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>280</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>first_enemy_in_lane</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>aoe_damage</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>130</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
@@ -1224,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1317,6 +1753,105 @@
         <v>1400</v>
       </c>
       <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>训练场</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>冠军竞技场</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2600</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>闪电赛</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>120</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
@@ -1335,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1514,6 +2049,324 @@
       </c>
       <c r="K3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>level_02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>skeletons</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>level_03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mini_pekka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>musketeer</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>baby_dragon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>level_04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>skeletons</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>mini_pekka</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>musketeer</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <dataValidations count="1">
@@ -1531,7 +2384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1767,6 +2620,150 @@
         <v>0.06</v>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mini_pekka_body</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>迷你皮卡</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D7" t="n">
+        <v>320</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F7">
+        <f>IF(E7&gt;0,D7/E7,"")</f>
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>musketeer_body</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>火枪手</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>340</v>
+      </c>
+      <c r="D8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F8">
+        <f>IF(E8&gt;0,D8/E8,"")</f>
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>skeleton_body</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>骷髅</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <f>IF(E9&gt;0,D9/E9,"")</f>
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>baby_dragon_body</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小龙</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>900</v>
+      </c>
+      <c r="D10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F10">
+        <f>IF(E10&gt;0,D10/E10,"")</f>
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>air</t>
         </is>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -782,7 +782,7 @@
         <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1437,20 +1437,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>direct_damage</t>
+          <t>aoe_damage</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>150</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>first_enemy_in_lane</t>
-        </is>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2751,7 +2749,7 @@
         <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F10">
         <f>IF(E10&gt;0,D10/E10,"")</f>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -447,8 +447,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
@@ -481,12 +481,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>move_speed_lane_per_s</t>
+          <t>move_speed_tiles_per_s</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>attack_range_lane_ratio</t>
+          <t>attack_range_tiles</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -521,10 +521,10 @@
         <v>1.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>1.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -620,10 +620,10 @@
         <v>1.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -686,10 +686,10 @@
         <v>1.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         <v>1.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.35</v>
+        <v>5.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
         <v>1.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.18</v>
+        <v>3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>300</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
         <v>140</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         <v>130</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         <v/>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2504,10 +2504,10 @@
         <v/>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         <v/>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         <v/>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2612,10 +2612,10 @@
         <v/>
       </c>
       <c r="G6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         <v/>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
         <v/>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.35</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
         <v/>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         <v/>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>0.18</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Levels'!$A$1:$I$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -449,8 +449,10 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,10 +493,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>aggro_radius_tiles</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>body_radius_tiles</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>unit_type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -526,12 +538,18 @@
       <c r="G2" t="n">
         <v>1.2</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>ground</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,12 +577,18 @@
       <c r="G3" t="n">
         <v>4.5</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>ground</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -592,12 +616,18 @@
       <c r="G4" t="n">
         <v>1.2</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>ground</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,12 +655,18 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>ground</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -658,12 +694,18 @@
       <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>air</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -691,12 +733,18 @@
       <c r="G7" t="n">
         <v>1.2</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>ground</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -724,12 +772,18 @@
       <c r="G8" t="n">
         <v>5.5</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>ground</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -757,12 +811,18 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>ground</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -790,17 +850,23 @@
       <c r="G10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>air</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:K1"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ground,air"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Levels'!$A$1:$I$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,8 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,6 +509,11 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>attack_targets</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -549,7 +555,12 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,7 +599,12 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -627,7 +643,12 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -666,7 +687,12 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -705,7 +731,12 @@
           <t>air</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -744,7 +775,12 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -783,7 +819,12 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -822,7 +863,12 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -861,13 +907,21 @@
           <t>air</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
-  <dataValidations count="1">
+  <autoFilter ref="A1:L1"/>
+  <dataValidations count="2">
     <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ground,air"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ground,air,both"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Levels'!$A$1:$I$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,9 @@
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,6 +516,16 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>death_spawn_unit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>death_spawn_count</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -561,6 +573,8 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,6 +619,8 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -649,6 +665,8 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -693,6 +711,8 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -737,6 +757,8 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -781,6 +803,8 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -825,6 +849,8 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -869,6 +895,8 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -913,9 +941,63 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>golem_body</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>石头人</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>goblin_body</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:N1"/>
   <dataValidations count="2">
     <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ground,air"</formula1>
@@ -934,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1313,6 +1395,54 @@
       </c>
       <c r="F15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>golem</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>石头人</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>治疗术</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1325,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1758,11 +1888,63 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>golem</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>golem_body</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>aoe_heal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"spawn_unit,direct_damage,aoe_damage"</formula1>
+      <formula1>"spawn_unit,direct_damage,aoe_damage,aoe_heal"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"first_enemy_in_lane"</formula1>
@@ -2502,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2887,6 +3069,42 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>golem_body</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>石头人</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F11">
+        <f>IF(E11&gt;0,D11/E11,"")</f>
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2899,7 +3117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3001,6 +3219,17 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aoe_heal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>食人魔</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>亡灵</t>
+          <t>怨灵</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>火球</t>
+          <t>火球术</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>射箭</t>
+          <t>箭雨</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>电击</t>
+          <t>电火花</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>迷你皮卡</t>
+          <t>狂战士</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>火枪手</t>
+          <t>女巫</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>骷髅海</t>
+          <t>骷髅兵</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>小龙</t>
+          <t>余烬火颅</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>闪电</t>
+          <t>闪电术</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>滚木</t>
+          <t>滚石</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>石头人</t>
+          <t>亡灵巨像</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>治疗术</t>
+          <t>治愈术</t>
         </is>
       </c>
       <c r="C17" t="n">

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -1960,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>rookie</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>训练场</t>
+          <t>试炼场</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>冠军竞技场</t>
+          <t>冠军赛</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>闪电赛</t>
+          <t>生死战</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>extreme</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2152,12 +2152,45 @@
         <v>1400</v>
       </c>
       <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>竞技场</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="1">
     <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"easy,normal,hard"</formula1>
+      <formula1>"rookie,easy,normal,hard,extreme"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2170,7 +2203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2666,6 +2699,112 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>level_05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>musketeer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
@@ -3117,7 +3256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3177,7 +3316,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>rookie</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3339,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>easy</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3354,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3367,22 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>extreme</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -1960,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2185,204 @@
         <v>1450</v>
       </c>
       <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>campaign_01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>战役1·部署</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>campaign_02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>战役2·圣水</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>180</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>campaign_03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>战役3·绕桥</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>campaign_04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>战役4·防守</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>campaign_05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>战役5·法术</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>180</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>campaign_06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>战役6·首领</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>180</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
@@ -2203,7 +2401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2805,6 +3003,642 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>campaign_01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>campaign_01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>skeletons</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>campaign_02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>campaign_02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>skeletons</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>campaign_03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>campaign_03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>skeletons</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>campaign_04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>campaign_04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>campaign_05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>campaign_05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>campaign_06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>goblins</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>campaign_06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>giant</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mini_pekka</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>musketeer</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>baby_dragon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>minions</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>arrows</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>archers</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Levels'!$A$1:$I$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -453,9 +453,11 @@
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,15 +518,25 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>splash_radius</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>target_priority</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>death_spawn_unit</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>death_spawn_count</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -575,6 +587,8 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -621,6 +635,8 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -665,8 +681,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -713,6 +735,8 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -759,6 +783,8 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -805,6 +831,8 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -851,6 +879,8 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -897,6 +927,8 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -940,9 +972,13 @@
           <t>both</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -986,24 +1022,33 @@
           <t>ground</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>goblin_body</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
-  <dataValidations count="2">
+  <autoFilter ref="A1:P1"/>
+  <dataValidations count="3">
     <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ground,air"</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ground,air,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"nearest,buildings"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -16,9 +16,9 @@
     <sheet name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Levels'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decks'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Balance_View'!$A$1:$I$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -455,9 +455,12 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,15 +531,30 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>on_hit_status_kind</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>on_hit_status_dur</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>on_hit_status_mag</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>death_spawn_unit</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>death_spawn_count</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -589,6 +607,9 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -637,6 +658,9 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,6 +713,9 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -737,6 +764,9 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -785,6 +815,9 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -833,6 +866,9 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -881,6 +917,9 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -929,6 +968,9 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -979,6 +1021,9 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1028,19 +1073,1489 @@
           <t>buildings</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>goblin_body</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>spear_goblin_body</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>长矛哥布林</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bat_body</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>血蝠</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>barbarian_body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>蛮兵</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>280</v>
+      </c>
+      <c r="D14" t="n">
+        <v>58</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ice_spirit_body</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>冰灵</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>60</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fire_spirit_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>火灵</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>electro_spirit_body</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>电灵</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>stun</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>squire_body</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>见习骑士</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>340</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>axe_thrower_body</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>掷斧手</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>160</v>
+      </c>
+      <c r="D19" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cave_spider_body</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>洞穴蛛</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bone_ram_body</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>亡骨冲车</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>650</v>
+      </c>
+      <c r="D21" t="n">
+        <v>120</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>skeleton_body</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>royal_giant_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>皇家巨像</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D22" t="n">
+        <v>150</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hog_rider_body</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>野猪骑士</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>120</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>valkyrie_body</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>瓦尔基里</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>900</v>
+      </c>
+      <c r="D24" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bomber_body</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>投弹亡灵</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>130</v>
+      </c>
+      <c r="D25" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mega_minion_body</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>巨型怨灵</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>340</v>
+      </c>
+      <c r="D26" t="n">
+        <v>120</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>battle_ram_body</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>战锤冲车</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>700</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>barbarian_body</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>wizard_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>巫师</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>340</v>
+      </c>
+      <c r="D28" t="n">
+        <v>130</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>executioner_body</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>行刑者</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>620</v>
+      </c>
+      <c r="D29" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>balloon_body</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>地狱气球</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D30" t="n">
+        <v>400</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>phoenix_body</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>不死凤凰</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>600</v>
+      </c>
+      <c r="D31" t="n">
+        <v>90</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>phoenix_reborn_body</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>phoenix_reborn_body</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>凤凰(重生)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>300</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>lava_hound_body</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>熔岩魔像</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D33" t="n">
+        <v>40</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>lava_pup_body</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>lava_pup_body</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>熔岩火犬</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>110</v>
+      </c>
+      <c r="D34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ice_wizard_body</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>寒冰法师</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>240</v>
+      </c>
+      <c r="D35" t="n">
+        <v>30</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>electro_wizard_body</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>电法师</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>340</v>
+      </c>
+      <c r="D36" t="n">
+        <v>90</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>stun</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>princess_body</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>公主</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>220</v>
+      </c>
+      <c r="D37" t="n">
+        <v>120</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>inferno_dragon_body</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>地狱飞龙</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>700</v>
+      </c>
+      <c r="D38" t="n">
+        <v>200</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:S1"/>
+  <dataValidations count="4">
     <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ground,air"</formula1>
     </dataValidation>
@@ -1049,6 +2564,9 @@
     </dataValidation>
     <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"nearest,buildings"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"slow,stun,freeze"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1061,7 +2579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1488,6 +3006,774 @@
       </c>
       <c r="F17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>spear_goblins</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>长矛哥布林</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bats</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>血蝠群</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>barbarians</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>蛮兵</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>minion_horde</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>怨灵大军</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ice_spirit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>冰灵</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fire_spirit</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>火灵</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>electro_spirit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>电灵</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>squire</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>见习骑士</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>axe_thrower</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>掷斧手</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cave_spiders</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>洞穴蛛群</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>rock_shower</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>石雨</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bone_ram</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>亡骨冲车</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>royal_giant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>皇家巨像</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hog_rider</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>野猪骑士</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>valkyrie</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>瓦尔基里</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bomber</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>投弹亡灵</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mega_minion</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>巨型怨灵</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>goblin_gang</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>哥布林帮</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>battle_ram</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>战锤冲车</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>giant_snowball</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>寒冰球</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>goblin_barrel</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>哥布林桶</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>巫师</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>executioner</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>行刑者</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>balloon</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>地狱气球</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>skeleton_army</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>骷髅大军</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>phoenix</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>不死凤凰</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>冰冻术</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>lava_hound</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>熔岩魔像</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ice_wizard</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>寒冰法师</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>electro_wizard</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>电法师</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>princess</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>公主</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>inferno_dragon</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>地狱飞龙</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>troop</t>
+        </is>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1500,7 +3786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1511,7 +3797,10 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1557,6 +3846,21 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>status_kind</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>status_dur</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>status_mag</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -1587,6 +3891,9 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1614,6 +3921,9 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1641,6 +3951,9 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1668,6 +3981,9 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1695,6 +4011,9 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1720,6 +4039,9 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1745,6 +4067,9 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1772,6 +4097,9 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1799,6 +4127,9 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1826,6 +4157,9 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1853,6 +4187,9 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1880,6 +4217,9 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1907,6 +4247,9 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1932,6 +4275,9 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1959,6 +4305,9 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1984,15 +4333,1047 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>spear_goblins</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>spear_goblin_body</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bats</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>bat_body</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>barbarians</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>barbarian_body</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>minion_horde</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>minion_body</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ice_spirit</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ice_spirit_body</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fire_spirit</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>fire_spirit_body</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>electro_spirit</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>electro_spirit_body</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>squire</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>squire_body</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>axe_thrower</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>axe_thrower_body</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cave_spiders</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>cave_spider_body</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>rock_shower</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>aoe_damage</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>125</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bone_ram</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>bone_ram_body</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>royal_giant</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>royal_giant_body</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hog_rider</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>hog_rider_body</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>valkyrie</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>valkyrie_body</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bomber</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>bomber_body</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mega_minion</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>mega_minion_body</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>goblin_gang</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>goblin_body</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>goblin_gang</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>spear_goblin_body</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>battle_ram</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>battle_ram_body</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>giant_snowball</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>aoe_damage</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>110</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>goblin_barrel</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>goblin_body</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>wizard_body</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>executioner</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>executioner_body</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>balloon</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>balloon_body</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>skeleton_army</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>skeleton_body</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>phoenix</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>phoenix_body</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>aoe_damage</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>lava_hound</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>lava_hound_body</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ice_wizard</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ice_wizard_body</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>electro_wizard</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>electro_wizard_body</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>electro_wizard</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>aoe_damage</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>90</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>princess</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>princess_body</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>inferno_dragon</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>spawn_unit</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>inferno_dragon_body</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <dataValidations count="2">
+  <autoFilter ref="A1:L1"/>
+  <dataValidations count="3">
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"spawn_unit,direct_damage,aoe_damage,aoe_heal"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"first_enemy_in_lane"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"slow,stun,freeze"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3702,7 +7083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4120,6 +7501,978 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>spear_goblin_body</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>长矛哥布林</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <f>IF(E12&gt;0,D12/E12,"")</f>
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bat_body</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>血蝠</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <f>IF(E13&gt;0,D13/E13,"")</f>
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>barbarian_body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>蛮兵</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>280</v>
+      </c>
+      <c r="D14" t="n">
+        <v>58</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F14">
+        <f>IF(E14&gt;0,D14/E14,"")</f>
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ice_spirit_body</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>冰灵</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>60</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f>IF(E15&gt;0,D15/E15,"")</f>
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fire_spirit_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>火灵</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <f>IF(E16&gt;0,D16/E16,"")</f>
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>electro_spirit_body</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>电灵</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <f>IF(E17&gt;0,D17/E17,"")</f>
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>squire_body</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>见习骑士</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>340</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F18">
+        <f>IF(E18&gt;0,D18/E18,"")</f>
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>axe_thrower_body</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>掷斧手</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>160</v>
+      </c>
+      <c r="D19" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F19">
+        <f>IF(E19&gt;0,D19/E19,"")</f>
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cave_spider_body</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>洞穴蛛</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <f>IF(E20&gt;0,D20/E20,"")</f>
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bone_ram_body</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>亡骨冲车</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>650</v>
+      </c>
+      <c r="D21" t="n">
+        <v>120</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F21">
+        <f>IF(E21&gt;0,D21/E21,"")</f>
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>royal_giant_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>皇家巨像</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D22" t="n">
+        <v>150</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F22">
+        <f>IF(E22&gt;0,D22/E22,"")</f>
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hog_rider_body</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>野猪骑士</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>120</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F23">
+        <f>IF(E23&gt;0,D23/E23,"")</f>
+        <v/>
+      </c>
+      <c r="G23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>valkyrie_body</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>瓦尔基里</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>900</v>
+      </c>
+      <c r="D24" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F24">
+        <f>IF(E24&gt;0,D24/E24,"")</f>
+        <v/>
+      </c>
+      <c r="G24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bomber_body</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>投弹亡灵</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>130</v>
+      </c>
+      <c r="D25" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F25">
+        <f>IF(E25&gt;0,D25/E25,"")</f>
+        <v/>
+      </c>
+      <c r="G25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mega_minion_body</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>巨型怨灵</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>340</v>
+      </c>
+      <c r="D26" t="n">
+        <v>120</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F26">
+        <f>IF(E26&gt;0,D26/E26,"")</f>
+        <v/>
+      </c>
+      <c r="G26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>battle_ram_body</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>战锤冲车</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>700</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F27">
+        <f>IF(E27&gt;0,D27/E27,"")</f>
+        <v/>
+      </c>
+      <c r="G27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>wizard_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>巫师</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>340</v>
+      </c>
+      <c r="D28" t="n">
+        <v>130</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F28">
+        <f>IF(E28&gt;0,D28/E28,"")</f>
+        <v/>
+      </c>
+      <c r="G28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>executioner_body</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>行刑者</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>620</v>
+      </c>
+      <c r="D29" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F29">
+        <f>IF(E29&gt;0,D29/E29,"")</f>
+        <v/>
+      </c>
+      <c r="G29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>balloon_body</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>地狱气球</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D30" t="n">
+        <v>400</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F30">
+        <f>IF(E30&gt;0,D30/E30,"")</f>
+        <v/>
+      </c>
+      <c r="G30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>phoenix_body</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>不死凤凰</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>600</v>
+      </c>
+      <c r="D31" t="n">
+        <v>90</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F31">
+        <f>IF(E31&gt;0,D31/E31,"")</f>
+        <v/>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>phoenix_reborn_body</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>凤凰(重生)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>300</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F32">
+        <f>IF(E32&gt;0,D32/E32,"")</f>
+        <v/>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>lava_hound_body</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>熔岩魔像</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D33" t="n">
+        <v>40</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F33">
+        <f>IF(E33&gt;0,D33/E33,"")</f>
+        <v/>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>lava_pup_body</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>熔岩火犬</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>110</v>
+      </c>
+      <c r="D34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <f>IF(E34&gt;0,D34/E34,"")</f>
+        <v/>
+      </c>
+      <c r="G34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ice_wizard_body</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>寒冰法师</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>240</v>
+      </c>
+      <c r="D35" t="n">
+        <v>30</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35">
+        <f>IF(E35&gt;0,D35/E35,"")</f>
+        <v/>
+      </c>
+      <c r="G35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>electro_wizard_body</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>电法师</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>340</v>
+      </c>
+      <c r="D36" t="n">
+        <v>90</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F36">
+        <f>IF(E36&gt;0,D36/E36,"")</f>
+        <v/>
+      </c>
+      <c r="G36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>princess_body</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>公主</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>220</v>
+      </c>
+      <c r="D37" t="n">
+        <v>120</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37">
+        <f>IF(E37&gt;0,D37/E37,"")</f>
+        <v/>
+      </c>
+      <c r="G37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>inferno_dragon_body</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>地狱飞龙</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>700</v>
+      </c>
+      <c r="D38" t="n">
+        <v>200</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <f>IF(E38&gt;0,D38/E38,"")</f>
+        <v/>
+      </c>
+      <c r="G38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>air</t>
         </is>
       </c>
     </row>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2552,6 +2552,114 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>golemite_body</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>石心魔像</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>400</v>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fire_pup_body</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>喷火火犬</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>110</v>
+      </c>
+      <c r="D40" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1"/>
@@ -7083,7 +7191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8471,6 +8579,78 @@
         <v>3.5</v>
       </c>
       <c r="I38" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>golemite_body</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>石心魔像</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>400</v>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F39">
+        <f>IF(E39&gt;0,D39/E39,"")</f>
+        <v/>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ground</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fire_pup_body</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>喷火火犬</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>110</v>
+      </c>
+      <c r="D40" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F40">
+        <f>IF(E40&gt;0,D40/E40,"")</f>
+        <v/>
+      </c>
+      <c r="G40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>air</t>
         </is>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$S$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Levels'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decks'!$A$1:$K$1</definedName>
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>骑士</t>
+          <t>虎贲校尉</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>弓箭手</t>
+          <t>魏武强弩手</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -670,7 +670,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>黄巾攻城力士</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>哥布林</t>
+          <t>山越短刀兵</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>亡灵</t>
+          <t>魂鸦</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>迷你皮卡</t>
+          <t>黑甲周仓</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -878,7 +878,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>火枪手</t>
+          <t>神射黄忠</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>骷髅</t>
+          <t>黄巾阴兵</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小龙</t>
+          <t>黄盖火龙鸢</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>石头人</t>
+          <t>江东镇岳巨械</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>长矛哥布林</t>
+          <t>山越投矛兵</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>血蝠</t>
+          <t>江东机关蜂</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>蛮兵</t>
+          <t>青州悍卒</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>冰灵</t>
+          <t>寒山符童</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>火灵</t>
+          <t>赤焰符童</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>电灵</t>
+          <t>雷符童子</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>见习骑士</t>
+          <t>虎贲新兵</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>掷斧手</t>
+          <t>巴郡飞斧手</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>洞穴蛛</t>
+          <t>巴蜀毒蛛</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>亡骨冲车</t>
+          <t>阴兵撞车</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>皇家巨像</t>
+          <t>刘晔霹雳车</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>野猪骑士</t>
+          <t>虎豹破城骑</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>瓦尔基里</t>
+          <t>山越旋刃卫</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>投弹亡灵</t>
+          <t>无当火油手</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>巨型怨灵</t>
+          <t>重甲机关隼</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>战锤冲车</t>
+          <t>青州撞城队</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>巫师</t>
+          <t>都督周瑜</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>行刑者</t>
+          <t>恶来典韦</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>地狱气球</t>
+          <t>孔明轰天灯</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>不死凤凰</t>
+          <t>庞统火鸾</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>凤凰(重生)</t>
+          <t>火鸾·重启</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>熔岩魔像</t>
+          <t>南蛮火鸢母兽</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>熔岩火犬</t>
+          <t>南蛮幼鸢</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>寒冰法师</t>
+          <t>冢虎司马懿</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>电法师</t>
+          <t>天公将军张角</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>公主</t>
+          <t>枭姬孙尚香</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>地狱飞龙</t>
+          <t>蜀汉火脉机关龙</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>石心魔像</t>
+          <t>石心攻城兽</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>喷火火犬</t>
+          <t>喷火小龙</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2687,15 +2687,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2711,20 +2712,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>faction</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>elixir_cost</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -2738,21 +2744,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>骑士</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+          <t>虎贲校尉</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2762,21 +2773,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>弓箭手</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>魏武强弩手</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2786,21 +2802,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>食人魔</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>黄巾攻城力士</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2810,21 +2831,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>哥布林</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+          <t>归附山越短刀兵</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2834,21 +2860,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>怨灵</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+          <t>魂鸦</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2858,21 +2889,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>火球术</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+          <t>赤壁火攻</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2882,21 +2918,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>箭雨</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+          <t>魏武箭阵</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2906,21 +2947,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>电火花</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+          <t>掌心雷</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2930,21 +2976,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>狂战士</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+          <t>黑甲周仓</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2954,21 +3005,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>女巫</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+          <t>神射黄忠</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>4</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2978,21 +3034,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>骷髅兵</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+          <t>黄巾阴兵</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3002,21 +3063,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>余烬火颅</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+          <t>黄盖火龙鸢</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3026,21 +3092,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>闪电术</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+          <t>于吉·五雷法</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3050,21 +3121,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>滚石</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+          <t>剑阁滚木</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3074,21 +3150,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>亡灵巨像</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+          <t>江东镇岳巨械</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>7</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3098,21 +3179,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>治愈术</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+          <t>荀彧·安军策</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3122,21 +3208,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>长矛哥布林</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+          <t>归附山越投矛兵</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>2</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3146,21 +3237,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>血蝠群</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+          <t>江东机关蜂</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3170,21 +3266,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>蛮兵</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+          <t>青州悍卒</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3194,21 +3295,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>怨灵大军</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+          <t>魂鸦大军</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3218,21 +3324,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>冰灵</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>寒山符童</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3242,21 +3353,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>火灵</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>赤焰符童</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3266,21 +3382,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>电灵</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>雷符童子</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3290,21 +3411,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>见习骑士</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+          <t>虎贲新兵</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3314,21 +3440,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>掷斧手</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+          <t>巴郡飞斧手</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3338,21 +3469,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>洞穴蛛群</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+          <t>巴蜀毒蛛</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3362,21 +3498,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>石雨</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+          <t>剑阁落石阵</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>2</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3386,21 +3527,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>亡骨冲车</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+          <t>阴兵撞车</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3410,21 +3556,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>皇家巨像</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+          <t>刘晔霹雳车</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3434,21 +3585,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>野猪骑士</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+          <t>虎豹破城骑</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>4</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3458,21 +3614,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>瓦尔基里</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+          <t>山越旋刃卫</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>4</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3482,21 +3643,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>投弹亡灵</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+          <t>无当火油手</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3506,21 +3672,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>巨型怨灵</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+          <t>重甲机关隼</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>3</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3530,21 +3701,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>哥布林帮</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+          <t>山越混编队</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3554,21 +3730,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>战锤冲车</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+          <t>青州撞城队</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>4</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3578,21 +3759,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>寒冰球</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+          <t>北地霜石</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E37" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3602,21 +3788,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>哥布林桶</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
+          <t>山越奇袭坛</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>3</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E38" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3626,21 +3817,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>巫师</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+          <t>都督周瑜</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>4</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E39" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3650,21 +3846,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>行刑者</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+          <t>恶来典韦</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E40" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3674,21 +3875,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>地狱气球</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+          <t>孔明轰天灯</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E41" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3698,21 +3904,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>骷髅大军</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+          <t>左慈·阴兵阵</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>4</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E42" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3722,21 +3933,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>不死凤凰</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
+          <t>庞统火鸾</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>4</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E43" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3746,21 +3962,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>冰冻术</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
+          <t>郭嘉·寒江计</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>4</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>spell</t>
         </is>
       </c>
-      <c r="E44" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3770,21 +3991,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>熔岩魔像</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
+          <t>南蛮火鸢母兽</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>7</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3794,21 +4020,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>寒冰法师</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
+          <t>冢虎司马懿</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>wei</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>3</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3818,21 +4049,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>电法师</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
+          <t>天公将军张角</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>qun</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>4</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E47" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3842,21 +4078,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>公主</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+          <t>枭姬孙尚香</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>3</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E48" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3866,24 +4107,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>地狱飞龙</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+          <t>蜀汉火脉机关龙</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>shu</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>4</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>troop</t>
         </is>
       </c>
-      <c r="E49" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:G1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"wei,shu,wu,qun"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7260,7 +7511,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>骑士</t>
+          <t>虎贲校尉</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7296,7 +7547,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>弓箭手</t>
+          <t>魏武强弩手</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -7332,7 +7583,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>黄巾攻城力士</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7368,7 +7619,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>哥布林</t>
+          <t>山越短刀兵</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -7404,7 +7655,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>亡灵</t>
+          <t>魂鸦</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -7440,7 +7691,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>迷你皮卡</t>
+          <t>黑甲周仓</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -7476,7 +7727,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>火枪手</t>
+          <t>神射黄忠</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -7512,7 +7763,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>骷髅</t>
+          <t>黄巾阴兵</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -7548,7 +7799,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小龙</t>
+          <t>黄盖火龙鸢</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -7584,7 +7835,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>石头人</t>
+          <t>江东镇岳巨械</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -7620,7 +7871,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>长矛哥布林</t>
+          <t>山越投矛兵</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -7656,7 +7907,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>血蝠</t>
+          <t>江东机关蜂</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -7692,7 +7943,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>蛮兵</t>
+          <t>青州悍卒</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -7728,7 +7979,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>冰灵</t>
+          <t>寒山符童</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -7764,7 +8015,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>火灵</t>
+          <t>赤焰符童</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -7800,7 +8051,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>电灵</t>
+          <t>雷符童子</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -7836,7 +8087,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>见习骑士</t>
+          <t>虎贲新兵</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -7872,7 +8123,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>掷斧手</t>
+          <t>巴郡飞斧手</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -7908,7 +8159,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>洞穴蛛</t>
+          <t>巴蜀毒蛛</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -7944,7 +8195,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>亡骨冲车</t>
+          <t>阴兵撞车</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -7980,7 +8231,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>皇家巨像</t>
+          <t>刘晔霹雳车</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -8016,7 +8267,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>野猪骑士</t>
+          <t>虎豹破城骑</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -8052,7 +8303,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>瓦尔基里</t>
+          <t>山越旋刃卫</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -8088,7 +8339,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>投弹亡灵</t>
+          <t>无当火油手</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -8124,7 +8375,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>巨型怨灵</t>
+          <t>重甲机关隼</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -8160,7 +8411,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>战锤冲车</t>
+          <t>青州撞城队</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -8196,7 +8447,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>巫师</t>
+          <t>都督周瑜</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -8232,7 +8483,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>行刑者</t>
+          <t>恶来典韦</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -8268,7 +8519,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>地狱气球</t>
+          <t>孔明轰天灯</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -8304,7 +8555,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>不死凤凰</t>
+          <t>庞统火鸾</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -8340,7 +8591,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>凤凰(重生)</t>
+          <t>火鸾·重启</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -8376,7 +8627,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>熔岩魔像</t>
+          <t>南蛮火鸢母兽</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -8412,7 +8663,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>熔岩火犬</t>
+          <t>南蛮幼鸢</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -8448,7 +8699,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>寒冰法师</t>
+          <t>冢虎司马懿</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -8484,7 +8735,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>电法师</t>
+          <t>天公将军张角</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -8520,7 +8771,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>公主</t>
+          <t>枭姬孙尚香</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -8556,7 +8807,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>地狱飞龙</t>
+          <t>蜀汉火脉机关龙</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -8592,7 +8843,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>石心魔像</t>
+          <t>石心攻城兽</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -8628,7 +8879,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>喷火火犬</t>
+          <t>喷火小龙</t>
         </is>
       </c>
       <c r="C40" t="n">

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -6282,7 +6282,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>royal_giant</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>minions</t>
+          <t>mega_minion</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="_Enums" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$T$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CardSkills'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Levels'!$A$1:$I$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,8 @@
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,6 +556,11 @@
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>vis_height_px</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -609,7 +615,10 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>48</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,7 +669,10 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>39</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -715,7 +727,10 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>74</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -766,7 +781,10 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>35</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,7 +835,10 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>39</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -868,7 +889,10 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>52</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -919,7 +943,10 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>44</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -970,7 +997,10 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>33</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1023,7 +1053,10 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>66</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1084,7 +1117,10 @@
       <c r="R11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>74</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1135,7 +1171,10 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>33</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1186,7 +1225,10 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>28</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1237,7 +1279,10 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>44</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1296,7 +1341,10 @@
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>31</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1349,7 +1397,10 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>31</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1406,7 +1457,10 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1457,7 +1511,10 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>39</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1508,7 +1565,10 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>37</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1559,7 +1619,10 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>31</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1620,7 +1683,10 @@
       <c r="R21" t="n">
         <v>2</v>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>54</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1675,7 +1741,10 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>70</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1730,7 +1799,10 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>48</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1783,7 +1855,10 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>48</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1836,7 +1911,10 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>35</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1887,7 +1965,10 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>42</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1948,7 +2029,10 @@
       <c r="R27" t="n">
         <v>2</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>52</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2001,7 +2085,10 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>42</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2054,7 +2141,10 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>46</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2109,7 +2199,10 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>57</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2166,7 +2259,10 @@
       <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>44</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2217,7 +2313,10 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>39</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2278,7 +2377,10 @@
       <c r="R33" t="n">
         <v>6</v>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>74</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2329,7 +2431,10 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>31</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2390,7 +2495,10 @@
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>39</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2447,7 +2555,10 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>42</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2500,7 +2611,10 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>37</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2551,7 +2665,10 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>46</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2606,7 +2723,10 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>44</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2659,10 +2779,13 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>31</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1"/>
+  <autoFilter ref="A1:T1"/>
   <dataValidations count="4">
     <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ground,air"</formula1>

--- a/config/GameConfig.xlsx
+++ b/config/GameConfig.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>虎贲校尉</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>魏武强弩手</t>
+          <t>兔射手</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -682,7 +682,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>黄巾攻城力士</t>
+          <t>大块头</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>山越短刀兵</t>
+          <t>小蟑螂</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>魂鸦</t>
+          <t>小乌鸦</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>黑甲周仓</t>
+          <t>锤锤莱姆</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -902,7 +902,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>神射黄忠</t>
+          <t>鼹鼠火枪手</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>黄巾阴兵</t>
+          <t>小骷髅</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>黄盖火龙鸢</t>
+          <t>龙宝宝</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>江东镇岳巨械</t>
+          <t>岩石史莱姆</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>山越投矛兵</t>
+          <t>蟑螂恶霸</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>江东机关蜂</t>
+          <t>小蝙蝠</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>青州悍卒</t>
+          <t>棒槌史莱姆</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>寒山符童</t>
+          <t>冰精灵</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>赤焰符童</t>
+          <t>火精灵</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>雷符童子</t>
+          <t>雷精灵</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>虎贲新兵</t>
+          <t>见习骑士</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>巴郡飞斧手</t>
+          <t>飞斧汪</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>巴蜀毒蛛</t>
+          <t>洞穴蜘蛛</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>阴兵撞车</t>
+          <t>骨头撞车</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刘晔霹雳车</t>
+          <t>瓜牛炮</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>虎豹破城骑</t>
+          <t>猪猪配香菇</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>山越旋刃卫</t>
+          <t>双斧火钳</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>无当火油手</t>
+          <t>猫炮手</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>重甲机关隼</t>
+          <t>鸦王</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>青州撞城队</t>
+          <t>攻城槌</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>都督周瑜</t>
+          <t>火法师</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>恶来典韦</t>
+          <t>回旋斧手</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>孔明轰天灯</t>
+          <t>马蜂王</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>庞统火鸾</t>
+          <t>火又鸟</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>火鸾·重启</t>
+          <t>火又鸟·重生</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南蛮火鸢母兽</t>
+          <t>幺蛾子</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>南蛮幼鸢</t>
+          <t>幼蛾子</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>冢虎司马懿</t>
+          <t>蝴蝶仙子</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>天公将军张角</t>
+          <t>雷法师</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>枭姬孙尚香</t>
+          <t>小公主</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>蜀汉火脉机关龙</t>
+          <t>熔岩龙</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>石心攻城兽</t>
+          <t>小岩史莱姆</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>虎贲校尉</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>魏武强弩手</t>
+          <t>兔射手</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>黄巾攻城力士</t>
+          <t>大块头</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>归附山越短刀兵</t>
+          <t>蟑螂小队</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>魂鸦</t>
+          <t>小乌鸦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>赤壁火攻</t>
+          <t>大火球</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>魏武箭阵</t>
+          <t>箭雨</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>掌心雷</t>
+          <t>电击术</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>黑甲周仓</t>
+          <t>锤锤莱姆</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>神射黄忠</t>
+          <t>鼹鼠火枪手</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>黄巾阴兵</t>
+          <t>小骷髅</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>黄盖火龙鸢</t>
+          <t>龙宝宝</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>于吉·五雷法</t>
+          <t>落雷</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>剑阁滚木</t>
+          <t>滚木</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>江东镇岳巨械</t>
+          <t>岩石史莱姆</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>荀彧·安军策</t>
+          <t>治疗术</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>归附山越投矛兵</t>
+          <t>投矛蟑螂</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>江东机关蜂</t>
+          <t>蝙蝠群</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>青州悍卒</t>
+          <t>棒槌史莱姆</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>魂鸦大军</t>
+          <t>乌鸦大军</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>寒山符童</t>
+          <t>冰精灵</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>赤焰符童</t>
+          <t>火精灵</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>雷符童子</t>
+          <t>雷精灵</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>虎贲新兵</t>
+          <t>见习骑士</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>巴郡飞斧手</t>
+          <t>飞斧汪</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>巴蜀毒蛛</t>
+          <t>洞穴蜘蛛</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>剑阁落石阵</t>
+          <t>落石</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>阴兵撞车</t>
+          <t>骨头撞车</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>刘晔霹雳车</t>
+          <t>瓜牛炮</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>虎豹破城骑</t>
+          <t>猪猪配香菇</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>山越旋刃卫</t>
+          <t>双斧火钳</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>无当火油手</t>
+          <t>猫炮手</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>重甲机关隼</t>
+          <t>鸦王</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>山越混编队</t>
+          <t>蟑螂恶霸帮</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>青州撞城队</t>
+          <t>攻城槌小队</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>北地霜石</t>
+          <t>大雪球</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>山越奇袭坛</t>
+          <t>蟑螂空投</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>都督周瑜</t>
+          <t>火法师</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>恶来典韦</t>
+          <t>回旋斧手</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>孔明轰天灯</t>
+          <t>马蜂王</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>左慈·阴兵阵</t>
+          <t>骷髅大军</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>庞统火鸾</t>
+          <t>火又鸟</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>郭嘉·寒江计</t>
+          <t>冰冻术</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>南蛮火鸢母兽</t>
+          <t>幺蛾子</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>冢虎司马懿</t>
+          <t>蝴蝶仙子</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>天公将军张角</t>
+          <t>雷法师</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>枭姬孙尚香</t>
+          <t>小公主</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>蜀汉火脉机关龙</t>
+          <t>熔岩龙</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>虎贲校尉</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>魏武强弩手</t>
+          <t>兔射手</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>黄巾攻城力士</t>
+          <t>大块头</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>山越短刀兵</t>
+          <t>小蟑螂</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>魂鸦</t>
+          <t>小乌鸦</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>黑甲周仓</t>
+          <t>锤锤莱姆</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>神射黄忠</t>
+          <t>鼹鼠火枪手</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>黄巾阴兵</t>
+          <t>小骷髅</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>黄盖火龙鸢</t>
+          <t>龙宝宝</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>江东镇岳巨械</t>
+          <t>岩石史莱姆</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>山越投矛兵</t>
+          <t>蟑螂恶霸</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>江东机关蜂</t>
+          <t>小蝙蝠</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>青州悍卒</t>
+          <t>棒槌史莱姆</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>寒山符童</t>
+          <t>冰精灵</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>赤焰符童</t>
+          <t>火精灵</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>雷符童子</t>
+          <t>雷精灵</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>虎贲新兵</t>
+          <t>见习骑士</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>巴郡飞斧手</t>
+          <t>飞斧汪</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>巴蜀毒蛛</t>
+          <t>洞穴蜘蛛</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>阴兵撞车</t>
+          <t>骨头撞车</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刘晔霹雳车</t>
+          <t>瓜牛炮</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>虎豹破城骑</t>
+          <t>猪猪配香菇</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>山越旋刃卫</t>
+          <t>双斧火钳</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>无当火油手</t>
+          <t>猫炮手</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>重甲机关隼</t>
+          <t>鸦王</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>青州撞城队</t>
+          <t>攻城槌</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>都督周瑜</t>
+          <t>火法师</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>恶来典韦</t>
+          <t>回旋斧手</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>孔明轰天灯</t>
+          <t>马蜂王</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>庞统火鸾</t>
+          <t>火又鸟</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>火鸾·重启</t>
+          <t>火又鸟·重生</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南蛮火鸢母兽</t>
+          <t>幺蛾子</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>南蛮幼鸢</t>
+          <t>幼蛾子</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>冢虎司马懿</t>
+          <t>蝴蝶仙子</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>天公将军张角</t>
+          <t>雷法师</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>枭姬孙尚香</t>
+          <t>小公主</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>蜀汉火脉机关龙</t>
+          <t>熔岩龙</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>石心攻城兽</t>
+          <t>小岩史莱姆</t>
         </is>
       </c>
       <c r="C39" t="n">
